--- a/data/trans_bre/IP16A02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 20,77</t>
+          <t>-15,64; 21,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 14,67</t>
+          <t>-23,34; 15,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 31,88</t>
+          <t>-7,67; 32,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 33,1</t>
+          <t>-9,28; 30,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,0; 108,62</t>
+          <t>-41,4; 117,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,65; 47,95</t>
+          <t>-43,98; 46,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 266,14</t>
+          <t>-22,81; 244,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 178,44</t>
+          <t>-25,39; 179,36</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,04; -7,83</t>
+          <t>-38,21; -8,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 26,94</t>
+          <t>-3,01; 28,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 11,4</t>
+          <t>-19,07; 10,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,68; 12,96</t>
+          <t>-25,51; 13,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,87; -17,6</t>
+          <t>-69,81; -20,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 98,73</t>
+          <t>-7,87; 108,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,28; 37,73</t>
+          <t>-40,01; 31,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,48; 33,69</t>
+          <t>-48,61; 31,49</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-28,82; 11,6</t>
+          <t>-28,41; 9,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 17,59</t>
+          <t>-15,85; 16,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 15,43</t>
+          <t>-21,34; 15,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 18,12</t>
+          <t>-40,95; 15,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,68; 34,65</t>
+          <t>-53,76; 28,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,62; 56,85</t>
+          <t>-34,55; 50,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,71; 48,65</t>
+          <t>-40,52; 45,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-70,01; 39,39</t>
+          <t>-73,58; 36,46</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 25,93</t>
+          <t>-13,22; 27,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 17,07</t>
+          <t>-14,81; 18,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 25,04</t>
+          <t>-9,61; 26,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 19,99</t>
+          <t>-21,46; 20,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,99; 85,31</t>
+          <t>-29,08; 98,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 57,27</t>
+          <t>-32,86; 60,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 103,79</t>
+          <t>-23,2; 112,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,96; 56,29</t>
+          <t>-38,81; 55,24</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 1,06</t>
+          <t>-18,63; 0,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 11,5</t>
+          <t>-5,55; 11,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 11,02</t>
+          <t>-7,22; 11,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 7,81</t>
+          <t>-21,18; 8,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 3,0</t>
+          <t>-40,44; 1,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 33,54</t>
+          <t>-13,26; 32,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 34,85</t>
+          <t>-17,78; 36,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-43,99; 18,62</t>
+          <t>-44,96; 21,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 21,79</t>
+          <t>-17,08; 20,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,34; 15,11</t>
+          <t>-24,34; 13,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 32,2</t>
+          <t>-6,11; 31,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 30,94</t>
+          <t>-6,66; 33,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,4; 117,32</t>
+          <t>-44,69; 109,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 46,45</t>
+          <t>-45,17; 42,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,81; 244,35</t>
+          <t>-20,08; 236,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-25,39; 179,36</t>
+          <t>-20,35; 208,18</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,21; -8,24</t>
+          <t>-38,89; -6,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 28,63</t>
+          <t>-2,99; 28,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 10,78</t>
+          <t>-19,67; 10,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 13,16</t>
+          <t>-25,44; 11,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,81; -20,59</t>
+          <t>-68,7; -15,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 108,34</t>
+          <t>-7,95; 112,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 31,92</t>
+          <t>-40,96; 32,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,61; 31,49</t>
+          <t>-48,25; 29,91</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-28,41; 9,51</t>
+          <t>-28,39; 12,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 16,07</t>
+          <t>-16,65; 16,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 15,63</t>
+          <t>-21,51; 15,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-40,95; 15,82</t>
+          <t>-44,8; 17,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,76; 28,6</t>
+          <t>-53,67; 34,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 50,47</t>
+          <t>-34,48; 53,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 45,95</t>
+          <t>-39,94; 43,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-73,58; 36,46</t>
+          <t>-72,46; 42,12</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 27,94</t>
+          <t>-16,87; 26,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 18,45</t>
+          <t>-12,75; 19,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 26,36</t>
+          <t>-11,84; 24,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,46; 20,06</t>
+          <t>-21,44; 20,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 98,8</t>
+          <t>-36,22; 88,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,86; 60,88</t>
+          <t>-26,83; 64,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 112,02</t>
+          <t>-27,27; 95,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,81; 55,24</t>
+          <t>-38,19; 60,72</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 0,56</t>
+          <t>-17,37; 1,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 11,33</t>
+          <t>-5,23; 12,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 11,68</t>
+          <t>-6,86; 11,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 8,71</t>
+          <t>-23,15; 7,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 1,45</t>
+          <t>-38,08; 3,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 32,22</t>
+          <t>-12,14; 33,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 36,04</t>
+          <t>-16,31; 37,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-44,96; 21,0</t>
+          <t>-47,8; 18,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,36</t>
+          <t>12,67</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,03%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 20,81</t>
+          <t>-16,72; 20,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 13,81</t>
+          <t>-23,41; 14,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 31,16</t>
+          <t>-6,77; 31,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 33,05</t>
+          <t>-8,77; 34,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,69; 109,45</t>
+          <t>-44,0; 108,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,17; 42,08</t>
+          <t>-43,65; 47,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 236,64</t>
+          <t>-21,27; 266,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,35; 208,18</t>
+          <t>-23,97; 181,68</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,45</t>
+          <t>-3,43</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-11,78%</t>
+          <t>-7,34%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,89; -6,4</t>
+          <t>-40,04; -7,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 28,96</t>
+          <t>-2,49; 26,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 10,64</t>
+          <t>-19,84; 11,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 11,74</t>
+          <t>-21,36; 14,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,7; -15,89</t>
+          <t>-69,87; -17,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 112,88</t>
+          <t>-6,02; 98,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,96; 32,7</t>
+          <t>-40,28; 37,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,25; 29,91</t>
+          <t>-38,85; 37,82</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-9,34</t>
+          <t>12,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-19,94%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 12,0</t>
+          <t>-28,82; 11,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 16,5</t>
+          <t>-13,72; 17,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 15,19</t>
+          <t>-23,57; 15,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-44,8; 17,28</t>
+          <t>-4,95; 33,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,67; 34,45</t>
+          <t>-55,68; 34,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 53,7</t>
+          <t>-29,62; 56,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-39,94; 43,95</t>
+          <t>-41,71; 48,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-72,46; 42,12</t>
+          <t>-8,61; 104,36</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,62</t>
+          <t>-2,64</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-3,38%</t>
+          <t>-5,31%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 26,06</t>
+          <t>-16,97; 25,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 19,44</t>
+          <t>-15,49; 17,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 24,01</t>
+          <t>-12,72; 25,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 20,98</t>
+          <t>-21,9; 19,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,22; 88,23</t>
+          <t>-37,99; 85,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 64,39</t>
+          <t>-32,67; 57,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,27; 95,7</t>
+          <t>-29,73; 103,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,19; 60,72</t>
+          <t>-39,1; 50,43</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,72</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-8,46%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 1,13</t>
+          <t>-18,03; 1,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 12,13</t>
+          <t>-5,29; 11,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 11,7</t>
+          <t>-6,67; 11,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 7,93</t>
+          <t>-4,44; 14,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,08; 3,03</t>
+          <t>-38,72; 3,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 33,94</t>
+          <t>-12,09; 33,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 37,0</t>
+          <t>-16,06; 34,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 18,84</t>
+          <t>-8,95; 37,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,08</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-5,34</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13,16</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,67</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-12,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,52%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>43,03%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.980787909472072</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-3.540688048250146</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.661021572960102</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.392473600783553</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.3500473736320697</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.4532777773428863</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.170146354120457</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.5893289450660725</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-16,72; 20,77</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-23,41; 14,67</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,77; 31,88</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-8,77; 34,13</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-44,0; 108,62</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-43,65; 47,95</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-21,27; 266,14</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-23,97; 181,68</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.697889646962132</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-8.357696395521568</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.053176212982746</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.966829775039415</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3882245589583062</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.8092294213965754</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.7264341142963324</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.3032877151382643</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.945358229472652</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.457911260609691</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.69888425684356</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.799570298359134</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.974351619704573</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.3812290641257554</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>11.10159164773194</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>2.531335353599915</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-22,91</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12,36</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-4,57</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-3,43</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-47,48%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>35,25%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-11,38%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-7,34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-40,04; -7,83</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,49; 26,94</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-19,84; 11,4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-21,36; 14,57</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-69,87; -17,6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-6,02; 98,73</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-40,28; 37,73</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-38,85; 37,82</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-3.986967850667057</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.678151008565185</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.7940233061620811</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.668366726545659</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.4244159592607212</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.281032622810816</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1568994653826748</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2391309227860775</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-9,28</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,6</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,09</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,54</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-20,74%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-6,97%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.073169834045469</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1683433499137083</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.677283157511134</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-7.835823964619807</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6836730504377365</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.003969420097194614</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5604204013910431</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5376629162950548</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-28,82; 11,6</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-13,72; 17,59</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-23,57; 15,43</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,95; 33,11</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-55,68; 34,65</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-29,62; 56,85</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-41,71; 48,65</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-8,61; 104,36</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-0.1100334968096472</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.865543838191964</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.342281565071052</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.993726300359471</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.04095049660184988</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>4.2906206805544</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.6865382314124402</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.2500118555408102</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,96</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,46</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,64</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,81%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-5,31%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-4.025559139123226</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.454131044971694</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.9545564972653304</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4.820465923334838</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.3833416570136501</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.4727177279785291</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.1623768862981222</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.3497776225596961</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-16,97; 25,93</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-15,49; 17,07</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-12,72; 25,04</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-21,9; 19,09</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-37,99; 85,31</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-32,67; 57,27</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-29,73; 103,79</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-39,1; 50,43</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.546688490070599</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.009571146989646</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.08876042555935</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.466547253611409</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.7021736775172679</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4934754590118269</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6336765233245462</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.1396927363374608</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.6382704490378129</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.049466942958228</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.747539421586855</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>11.63274340757082</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1114073329254241</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2.997987596514388</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.7781193261009952</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.134642588984583</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.874681407861099</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.518548307418059</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9202905810387195</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.8812035354495054</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2591039393091999</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3094277856390671</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.3124449710461079</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.09510086454675477</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-6.022973363782135</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-6.619769168085228</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.400169918509928</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-6.491692384353286</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6423607359749032</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6490976899212787</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5457454749993557</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5165699317591258</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.28329213423165</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.517793422854105</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.922052824836296</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.260864660726367</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.4292892968276585</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.299490654486167</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.642785886918732</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.671292254663445</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-8,28</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,73</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-20,08%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-18,03; 1,06</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-5,29; 11,5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-6,67; 11,02</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,44; 14,82</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-38,72; 3,0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-12,09; 33,54</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-16,06; 34,85</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-8,95; 37,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-2.147550396462416</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.0026693380173963</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1309507165159936</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.7304544966082599</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2615357865625642</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.0004957879606828764</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.03325226120339658</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.07050705099158684</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-4.367374475053996</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.913559872394029</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.519951932790151</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.24043303881145</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4574221769685463</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3068954220078444</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3174816945821887</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1881747554229367</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.04272646517852274</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.157082612305553</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.701109120780015</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.439527584093203</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.008211232221986156</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.4987000980050025</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.5375322164996861</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.3974714982335945</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
